--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_23-10-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_23-10-2025.xlsx
@@ -528,17 +528,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -576,25 +576,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,25 +687,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -798,25 +798,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -861,17 +861,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -909,25 +909,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -972,17 +972,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1020,25 +1020,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1131,25 +1131,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1242,25 +1242,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1353,25 +1353,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1464,25 +1464,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1575,25 +1575,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1686,25 +1686,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1797,25 +1797,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1860,17 +1860,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1908,25 +1908,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2019,25 +2019,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2130,25 +2130,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff79b56e8e5+80021]
+	GetHandleVerifier [0x0x7ff79b56e940+80112]
+	(No symbol) [0x0x7ff79b2f060f]
+	(No symbol) [0x0x7ff79b348854]
+	(No symbol) [0x0x7ff79b348b1c]
+	(No symbol) [0x0x7ff79b39c927]
+	(No symbol) [0x0x7ff79b37126f]
+	(No symbol) [0x0x7ff79b39968a]
+	(No symbol) [0x0x7ff79b371003]
+	(No symbol) [0x0x7ff79b3395d1]
+	(No symbol) [0x0x7ff79b33a3f3]
+	GetHandleVerifier [0x0x7ff79b82dc7d+2960429]
+	GetHandleVerifier [0x0x7ff79b827f3a+2936554]
+	GetHandleVerifier [0x0x7ff79b848977+3070247]
+	GetHandleVerifier [0x0x7ff79b5883ce+185214]
+	GetHandleVerifier [0x0x7ff79b58fe1f+216527]
+	GetHandleVerifier [0x0x7ff79b577b24+117460]
+	GetHandleVerifier [0x0x7ff79b577cdf+117903]
+	GetHandleVerifier [0x0x7ff79b55dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
